--- a/review_test_cases/13_test_for_techreview3/techreview2version_smallfix.xlsx
+++ b/review_test_cases/13_test_for_techreview3/techreview2version_smallfix.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HydrogenRb\HydrogenRb\Work\tech\Agent\8_14\review_test_cases\13_test_for_techreview3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8989D2F-2F29-45D5-96BD-FD34981DAD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7393D316-4D41-4A53-A723-555EBFC1927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="集成" sheetId="1" r:id="rId1"/>
+    <sheet name="集成_RISCV_TOP" sheetId="1" r:id="rId1"/>
     <sheet name="RISCV_TOP" sheetId="2" r:id="rId2"/>
     <sheet name="RISCV_CORE_TEST" sheetId="3" r:id="rId3"/>
     <sheet name="MEM_PHY" sheetId="4" r:id="rId4"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="111">
   <si>
     <t>分类</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -268,10 +268,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>`LANE_NUM * `Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3*100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -452,6 +448,38 @@
   </si>
   <si>
     <t>NA[i]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verification_sig_{{i}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For verif</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DW_VERI_{{i}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i的范围是{dat,req,reqext}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`APB_1_MEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`LANE_NUM_MEM * `Test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`DW_VERI_{{i}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verification_sig_{{i}}_tie0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -805,7 +833,7 @@
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I1" s="2"/>
       <c r="L1" s="2" t="s">
@@ -818,7 +846,7 @@
       <c r="O1" s="2"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R1" s="2"/>
       <c r="S1" s="2" t="s">
@@ -922,7 +950,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -955,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="S3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T3" t="s">
         <v>20</v>
@@ -991,7 +1019,7 @@
     <row r="4" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -1016,13 +1044,13 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
+        <v>101</v>
+      </c>
+      <c r="R4" t="s">
+        <v>20</v>
+      </c>
+      <c r="S4" t="s">
         <v>102</v>
-      </c>
-      <c r="R4" t="s">
-        <v>20</v>
-      </c>
-      <c r="S4" t="s">
-        <v>103</v>
       </c>
       <c r="X4" s="2"/>
       <c r="Y4" t="s">
@@ -1049,7 +1077,7 @@
     <row r="5" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -1098,7 +1126,7 @@
     <row r="6" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A6" s="2"/>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1282,10 +1310,10 @@
         <v>5</v>
       </c>
       <c r="K10" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" t="s">
         <v>93</v>
-      </c>
-      <c r="L10" t="s">
-        <v>94</v>
       </c>
       <c r="M10" t="s">
         <v>5</v>
@@ -1314,6 +1342,21 @@
       <c r="G11" t="s">
         <v>5</v>
       </c>
+      <c r="K11" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" t="s">
+        <v>103</v>
+      </c>
+      <c r="O11" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A12" s="2"/>
@@ -1431,16 +1474,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
         <v>60</v>
       </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -1449,13 +1492,13 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -1464,13 +1507,13 @@
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="2"/>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
         <v>20</v>
@@ -1478,16 +1521,16 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" t="s">
         <v>72</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" t="s">
-        <v>73</v>
       </c>
       <c r="I26" t="s">
         <v>5</v>
@@ -1496,7 +1539,7 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="2"/>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -1535,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{202D62A6-CB45-4A21-B036-6EE2427F8DDC}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="23.06640625" customWidth="1"/>
@@ -1774,10 +1817,10 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s">
         <v>87</v>
-      </c>
-      <c r="E21" t="s">
-        <v>88</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
@@ -1826,28 +1869,28 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
         <v>60</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="2"/>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -1856,7 +1899,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="2"/>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1864,13 +1907,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
         <v>73</v>
-      </c>
-      <c r="D31" t="s">
-        <v>74</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -1882,19 +1925,39 @@
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="2"/>
       <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
         <v>75</v>
       </c>
-      <c r="D32" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" t="s">
-        <v>76</v>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1913,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F3E398-7E0A-4C3A-A273-DA12B1D3ED24}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="37.06640625" customWidth="1"/>
@@ -1955,13 +2018,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
         <v>86</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>88</v>
       </c>
       <c r="I3" t="s">
         <v>50</v>
@@ -1970,7 +2033,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1979,7 +2042,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1993,7 +2056,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2008,7 +2071,7 @@
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2142,7 +2205,7 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -2219,7 +2282,7 @@
         <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -2274,10 +2337,10 @@
         <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F34" t="s">
         <v>20</v>
@@ -2286,13 +2349,13 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="2"/>
       <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" t="s">
         <v>67</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>68</v>
-      </c>
-      <c r="E35" t="s">
-        <v>69</v>
       </c>
       <c r="F35" t="s">
         <v>20</v>
@@ -2300,28 +2363,28 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" t="s">
         <v>60</v>
       </c>
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="I37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="2"/>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
@@ -2330,7 +2393,7 @@
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="2"/>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -2338,16 +2401,36 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s">
         <v>93</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>94</v>
       </c>
-      <c r="D41" t="s">
-        <v>95</v>
-      </c>
       <c r="F41" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2451,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F2DC5A-AAE7-49CB-BE38-CB832B2EDA63}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
@@ -2415,9 +2498,6 @@
       <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
@@ -2433,9 +2513,6 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
@@ -2539,7 +2616,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -2690,16 +2767,16 @@
         <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
@@ -2734,27 +2811,44 @@
         <v>56</v>
       </c>
       <c r="D31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" t="s">
         <v>57</v>
       </c>
-      <c r="E31" t="s">
-        <v>58</v>
-      </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2777,7 +2871,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
         <v>35</v>
@@ -2811,10 +2905,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2826,19 +2920,19 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
         <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2857,7 +2951,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
@@ -2891,7 +2985,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -2906,16 +3000,16 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
         <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
